--- a/activity_log.xlsx
+++ b/activity_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-11 13:06:49</t>
+          <t>2026-04-13 15:29:05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,217 +468,217 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Session started by 'Enzo Maverick'</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-11 13:07:35</t>
+          <t>2026-04-13 15:43:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PUT WAREHOUSE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hostname: PS-2044 | Shelf: Area C</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11 13:07:51</t>
+          <t>2026-04-13 15:44:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNSTAGE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hostname: PS-2044 | Shelf: Area C</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-11 13:07:56</t>
+          <t>2026-04-13 15:45:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PUT WAREHOUSE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hostname: PS-2044 | Shelf: Area C</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:38</t>
+          <t>2026-04-13 15:46:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNSTAGE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hostname: PS-2000 | Shelf: Area B</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:41</t>
+          <t>2026-04-13 16:09:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNSTAGE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hostname: PS-2012 | Shelf: Area B</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:44</t>
+          <t>2026-04-13 16:10:38</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNSTAGE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hostname: PS-2121 | Shelf: Area B</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:46</t>
+          <t>2026-04-13 16:17:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNSTAGE</t>
+          <t>PUT WAREHOUSE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hostname: PS-2122 | Shelf: Area B</t>
+          <t>[W2] Set: SET-001 | Items: 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:48</t>
+          <t>2026-04-13 16:19:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNSTAGE</t>
+          <t>PUT WAREHOUSE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hostname: PS-2044 | Shelf: Area C</t>
+          <t>[W2] Set: SET-002 | Items: 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:54</t>
+          <t>2026-04-13 16:27:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PUT WAREHOUSE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hostname: PS-2000 | Shelf: Area B</t>
+          <t>Session started by 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:54</t>
+          <t>2026-04-13 16:28:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,19 +688,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hostname: PS-2012 | Shelf: Area B</t>
+          <t>[W1] Hostname: PS-0142 | Shelf: Area A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-11 13:09:54</t>
+          <t>2026-04-13 16:28:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Enzo Maverick</t>
+          <t>Mark Benjamin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,117 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hostname: PS-2121 | Shelf: Area B</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-04-11 13:09:54</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Enzo Maverick</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PUT WAREHOUSE</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Hostname: PS-2122 | Shelf: Area B</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-04-11 13:09:54</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Enzo Maverick</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PUT WAREHOUSE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Hostname: PS-2044 | Shelf: Area C</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-04-11 13:10:50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Enzo Maverick</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PUT WAREHOUSE</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Hostname: PS-1987 | Shelf: Area C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-04-11 13:10:50</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Enzo Maverick</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PUT WAREHOUSE</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Hostname: PS-1900 | Shelf: Area C</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-04-11 13:12:01</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Enzo Maverick</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SHELF STATUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Shelf: Area B → FULL</t>
+          <t>[W1] Hostname: PS-0111 | Shelf: Area A</t>
         </is>
       </c>
     </row>

--- a/activity_log.xlsx
+++ b/activity_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13 15:29:05</t>
+          <t>2026-04-14 08:20:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-13 15:43:09</t>
+          <t>2026-04-14 08:20:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-13 15:44:24</t>
+          <t>2026-04-14 08:20:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,19 +507,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOGIN</t>
+          <t>LOGOUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Session started by 'Mark Benjamin'</t>
+          <t>Session ended for 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:36</t>
+          <t>2026-04-14 08:21:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:13</t>
+          <t>2026-04-14 08:22:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOGIN</t>
+          <t>UNSTAGE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Session started by 'Mark Benjamin'</t>
+          <t>[W2] Set: SET-001 | Item: Headset | Shelf: Area C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-13 16:09:09</t>
+          <t>2026-04-14 08:22:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOGIN</t>
+          <t>UNSTAGE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Session started by 'Mark Benjamin'</t>
+          <t>[W2] Set: SET-001 | Item: Monitor | Shelf: Area A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-13 16:10:38</t>
+          <t>2026-04-14 08:24:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,122 +595,3070 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOGIN</t>
+          <t>LOGOUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Session started by 'Mark Benjamin'</t>
+          <t>Session ended for 'Mark Benjamin'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-13 16:17:42</t>
+          <t>2026-04-14 08:24:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mark Benjamin</t>
+          <t>Andrea Alcalde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PUT WAREHOUSE</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[W2] Set: SET-001 | Items: 1</t>
+          <t>Session started by 'Andrea Alcalde'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-13 16:19:34</t>
+          <t>2026-04-14 08:24:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mark Benjamin</t>
+          <t>Andrea Alcalde</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PUT WAREHOUSE</t>
+          <t>UNSTAGE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[W2] Set: SET-002 | Items: 2</t>
+          <t>[W1] Hostname: PS-0111 | Shelf: Area A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-13 16:27:20</t>
+          <t>2026-04-14 08:24:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mark Benjamin</t>
+          <t>Andrea Alcalde</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LOGIN</t>
+          <t>UNSTAGE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Session started by 'Mark Benjamin'</t>
+          <t>[W1] Hostname: PS-0142 | Shelf: Area A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-13 16:28:12</t>
+          <t>2026-04-14 08:26:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mark Benjamin</t>
+          <t>Andrea Alcalde</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PUT WAREHOUSE</t>
+          <t>LOGOUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[W1] Hostname: PS-0142 | Shelf: Area A</t>
+          <t>Session ended for 'Andrea Alcalde'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-13 16:28:12</t>
+          <t>2026-04-14 08:26:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mark Benjamin</t>
+          <t>Andrea Alclade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea Alclade'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:31:04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Andrea Alclade</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea Alclade'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:31:31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:32:07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:37:14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:37:28</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:40:21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:46:22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-14 11:35:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-14 11:47:14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-14 11:47:30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Diana Padullo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Session started by 'Diana Padullo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-14 11:50:48</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Diana Padullo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>PUT WAREHOUSE</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>[W1] Hostname: PS-0111 | Shelf: Area A</t>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-14 12:48:17</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Diana Padullo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Session ended for 'Diana Padullo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:07:34</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:08:22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:10:07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:10:07</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2021 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:10:07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2031 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:10:07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2041 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:10:07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2051 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:11:43</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Items: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:13:09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2999 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:40:44</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:40:54</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:42:13</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2051 | Shelf: Area B | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:42:21</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2031 | Shelf: Area B | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:51:50</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:55:49</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:59:55</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:00:15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:07:47</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:08:09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:14:38</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:36:03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:44:49</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:45:09</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-17 19:00:55</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-17 19:11:43</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-17 19:22:14</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-17 19:22:43</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-17 19:23:14</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-17 19:24:07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:04:39</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-18 00:09:47</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-18 00:21:33</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Mark Benjamin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark Benjamin'</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:36:31</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:37:35</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Andrea Alcalde</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea Alcalde'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:41:23</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:41:53</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2041 | Shelf: Area B | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:47:35</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:47:45</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:53:15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-002 | Items: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:57:42</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:57:56</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-18 06:58:28</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2001 | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:00:05</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-0211 | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:01:22</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:02:22</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea'</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:03:01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-0211 | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:03:09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-0211 | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:04:38</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2001 | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:04:42</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2001 | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:06:32</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea'</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:07:09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:08:35</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:08:46</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:09:35</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-003 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:09:59</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-003 | Item: Monitor | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:10:20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2001 | Shelf: Area D | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:19:39</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:19:53</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:26:04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:26:19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:26:55</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:27:25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:33:58</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:36:25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:37:27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:40:01</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:40:14</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:41:49</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Kim Gonzales</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim Gonzales'</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:42:05</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:42:39</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-003 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:45:02</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:45:23</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:45:42</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-003 | Item: Monitor | Shelf: Area C</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:45:46</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-003 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:47:19</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:47:26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:47:35</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-18 11:47:40</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:01:24</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:01:35</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:03:53</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:04:01</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Session started by 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:04:13</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Session ended for 'Kim'</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:58:19</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Session started by 'Benj'</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:59:29</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2009 | Shelf: Area C</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:00:39</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2009 | Shelf: Area C</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:03:50</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Session ended for 'Benj'</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:05:04</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Session started by 'Benj'</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:05:12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:05:22</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:05:34</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>UPDATE ITEM</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:06:52</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>UPDATE ITEM</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:07:12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1 | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:08:06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SHELF STATUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Shelf: Area A → FULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:08:20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SHELF STATUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Shelf: Area A → AVAILABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:08:36</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>UNDO PULL</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:08:41</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:08:45</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:09:23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Session ended for 'Benj'</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:09:23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Session started by 'Andrea'</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:09:35</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Item: Mouse | Shelf: Area C</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:09:52</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:10:12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SHELF STATUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>[W2] Shelf: Area A → FULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:10:27</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SHELF STATUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>[W2] Shelf: Area A → AVAILABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:10:34</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Item: Monitor | Shelf: Area C</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:10:52</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:11:18</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-002 | Item: Keyboard | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-002 | Item: Mouse | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:14</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-002 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:22</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-002 | Item: Mouse | Shelf: Area D</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:30</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-002 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:37</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-002 | Item: Mouse | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:13:44</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2021 | Shelf: Area B</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:14:05</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Session ended for 'Andrea'</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:18:30</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Session started by 'Benj'</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:18:42</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Item: Monitor | Shelf: Area C</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-19 11:02:44</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Session ended for 'Benj'</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-19 11:05:28</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Session started by 'Mark'</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-19 11:05:35</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>UNSTAGE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Item: Mouse | Shelf: Area C</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-19 11:05:46</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PUT WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>[W2] Set: SET-001 | Items: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-19 11:07:17</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>WAREHOUSE PULL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>[W1] Hostname: PS-2011 | Shelf: Rack 1 - Bay 1 | Reason: Shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-19 11:11:19</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Session ended for 'Mark'</t>
         </is>
       </c>
     </row>
